--- a/backtest_runs/20260410_193731/by_symbol/OBOY/OBOY.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/OBOY/OBOY.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>-12270</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>100490.8</v>
@@ -817,7 +817,7 @@
         <v>-1717.799999999985</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>109202.5</v>
@@ -909,7 +909,7 @@
         <v>-5644.199999999989</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>103926.4</v>
@@ -1001,7 +1001,7 @@
         <v>-490.8000000000113</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>104417.2</v>
@@ -1047,7 +1047,7 @@
         <v>-245.3999999999948</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>104171.8</v>
@@ -1185,7 +1185,7 @@
         <v>-4171.799999999998</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>105766.9</v>
@@ -1277,7 +1277,7 @@
         <v>-4417.200000000004</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>101963.2</v>
@@ -1415,7 +1415,7 @@
         <v>-1717.800000000007</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>104539.9</v>
@@ -1461,7 +1461,7 @@
         <v>-245.3999999999948</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>104294.5</v>
@@ -1553,7 +1553,7 @@
         <v>-1104.299999999998</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>103681</v>
@@ -1645,7 +1645,7 @@
         <v>-2944.800000000002</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>111165.7</v>
